--- a/tutorials/Draft/Table.xlsx
+++ b/tutorials/Draft/Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deyve\Documents\PySonoGen\tutorials\Draft\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INSERM\Documents\Esteban\PyField\tutorials\Draft\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8DB4C6E-5324-482B-AEAB-E3BE4CD1EBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169E15B5-C3DD-4D94-B3E0-759ECAB92814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C3599692-E6F5-48F0-8CA3-3A85ED04EF7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3599692-E6F5-48F0-8CA3-3A85ED04EF7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -212,9 +212,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,13 +549,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD268210-B4AD-4D89-8072-76E81E3861F0}">
   <dimension ref="B2:U11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="19" width="12.59765625" customWidth="1"/>
+    <col min="2" max="19" width="12.5703125" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="F2" s="1"/>
@@ -573,40 +572,40 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="2:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="2:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="2:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
@@ -615,30 +614,30 @@
         <v>18</v>
       </c>
       <c r="G4" s="7"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4" t="s">
+      <c r="L4" s="4"/>
+      <c r="M4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4" t="s">
+      <c r="N4" s="3"/>
+      <c r="O4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4" t="s">
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="4"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="8"/>
     </row>
-    <row r="5" spans="2:21" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
@@ -673,60 +672,55 @@
         <v>13</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="9"/>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="S11" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="N3:S3"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="S3:S4"/>
     <mergeCell ref="D3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
